--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775966</v>
+        <v>121775974</v>
       </c>
       <c r="B47" t="n">
-        <v>78352</v>
+        <v>56561</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751517</v>
+        <v>751410</v>
       </c>
       <c r="R47" t="n">
-        <v>7264897</v>
+        <v>7264890</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775974</v>
+        <v>121775963</v>
       </c>
       <c r="B48" t="n">
-        <v>56561</v>
+        <v>78353</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751410</v>
+        <v>751417</v>
       </c>
       <c r="R48" t="n">
-        <v>7264890</v>
+        <v>7264910</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775975</v>
+        <v>121775990</v>
       </c>
       <c r="B49" t="n">
-        <v>90110</v>
+        <v>78261</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5497,25 +5497,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5685</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751479</v>
+        <v>751420</v>
       </c>
       <c r="R49" t="n">
-        <v>7264948</v>
+        <v>7264903</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775983</v>
+        <v>121775978</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751495</v>
+        <v>751407</v>
       </c>
       <c r="R50" t="n">
-        <v>7264900</v>
+        <v>7264897</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5689,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775959</v>
+        <v>121775975</v>
       </c>
       <c r="B51" t="n">
-        <v>57373</v>
+        <v>90110</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5701,25 +5701,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751541</v>
+        <v>751479</v>
       </c>
       <c r="R51" t="n">
-        <v>7264963</v>
+        <v>7264948</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775973</v>
+        <v>121775983</v>
       </c>
       <c r="B52" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751549</v>
+        <v>751495</v>
       </c>
       <c r="R52" t="n">
-        <v>7264968</v>
+        <v>7264900</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775977</v>
+        <v>121775973</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751406</v>
+        <v>751549</v>
       </c>
       <c r="R53" t="n">
-        <v>7264892</v>
+        <v>7264968</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775978</v>
+        <v>121775966</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751407</v>
+        <v>751517</v>
       </c>
       <c r="R54" t="n">
         <v>7264897</v>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775963</v>
+        <v>121775976</v>
       </c>
       <c r="B55" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,21 +6113,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751417</v>
+        <v>751492</v>
       </c>
       <c r="R55" t="n">
-        <v>7264910</v>
+        <v>7264960</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775976</v>
+        <v>121775959</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751492</v>
+        <v>751541</v>
       </c>
       <c r="R56" t="n">
-        <v>7264960</v>
+        <v>7264963</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775990</v>
+        <v>121775977</v>
       </c>
       <c r="B57" t="n">
-        <v>78261</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751420</v>
+        <v>751406</v>
       </c>
       <c r="R57" t="n">
-        <v>7264903</v>
+        <v>7264892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775959</v>
+        <v>121775977</v>
       </c>
       <c r="B56" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751541</v>
+        <v>751406</v>
       </c>
       <c r="R56" t="n">
-        <v>7264963</v>
+        <v>7264892</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775977</v>
+        <v>121775959</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751406</v>
+        <v>751541</v>
       </c>
       <c r="R57" t="n">
-        <v>7264892</v>
+        <v>7264963</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775974</v>
+        <v>121775976</v>
       </c>
       <c r="B47" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751410</v>
+        <v>751492</v>
       </c>
       <c r="R47" t="n">
-        <v>7264890</v>
+        <v>7264960</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775963</v>
+        <v>121775990</v>
       </c>
       <c r="B48" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751417</v>
+        <v>751420</v>
       </c>
       <c r="R48" t="n">
-        <v>7264910</v>
+        <v>7264903</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775990</v>
+        <v>121775966</v>
       </c>
       <c r="B49" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751420</v>
+        <v>751517</v>
       </c>
       <c r="R49" t="n">
-        <v>7264903</v>
+        <v>7264897</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775978</v>
+        <v>121775973</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751407</v>
+        <v>751549</v>
       </c>
       <c r="R50" t="n">
-        <v>7264897</v>
+        <v>7264968</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775975</v>
+        <v>121775977</v>
       </c>
       <c r="B51" t="n">
-        <v>90110</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5701,25 +5701,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751479</v>
+        <v>751406</v>
       </c>
       <c r="R51" t="n">
-        <v>7264948</v>
+        <v>7264892</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775983</v>
+        <v>121775963</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751495</v>
+        <v>751417</v>
       </c>
       <c r="R52" t="n">
-        <v>7264900</v>
+        <v>7264910</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775973</v>
+        <v>121775959</v>
       </c>
       <c r="B53" t="n">
-        <v>56561</v>
+        <v>57373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,16 +5909,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751549</v>
+        <v>751541</v>
       </c>
       <c r="R53" t="n">
-        <v>7264968</v>
+        <v>7264963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775966</v>
+        <v>121775978</v>
       </c>
       <c r="B54" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751517</v>
+        <v>751407</v>
       </c>
       <c r="R54" t="n">
         <v>7264897</v>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,7 +6097,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775976</v>
+        <v>121775983</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751492</v>
+        <v>751495</v>
       </c>
       <c r="R55" t="n">
-        <v>7264960</v>
+        <v>7264900</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6167,12 +6167,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775977</v>
+        <v>121775975</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>90110</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6211,25 +6211,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751406</v>
+        <v>751479</v>
       </c>
       <c r="R56" t="n">
-        <v>7264892</v>
+        <v>7264948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775959</v>
+        <v>121775974</v>
       </c>
       <c r="B57" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751541</v>
+        <v>751410</v>
       </c>
       <c r="R57" t="n">
-        <v>7264963</v>
+        <v>7264890</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775976</v>
+        <v>121775963</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751492</v>
+        <v>751417</v>
       </c>
       <c r="R47" t="n">
-        <v>7264960</v>
+        <v>7264910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775990</v>
+        <v>121775959</v>
       </c>
       <c r="B48" t="n">
-        <v>78261</v>
+        <v>57373</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751420</v>
+        <v>751541</v>
       </c>
       <c r="R48" t="n">
-        <v>7264903</v>
+        <v>7264963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775966</v>
+        <v>121775983</v>
       </c>
       <c r="B49" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751517</v>
+        <v>751495</v>
       </c>
       <c r="R49" t="n">
-        <v>7264897</v>
+        <v>7264900</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775973</v>
+        <v>121775977</v>
       </c>
       <c r="B50" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751549</v>
+        <v>751406</v>
       </c>
       <c r="R50" t="n">
-        <v>7264968</v>
+        <v>7264892</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775977</v>
+        <v>121775973</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,21 +5705,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751406</v>
+        <v>751549</v>
       </c>
       <c r="R51" t="n">
-        <v>7264892</v>
+        <v>7264968</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775963</v>
+        <v>121775976</v>
       </c>
       <c r="B52" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751417</v>
+        <v>751492</v>
       </c>
       <c r="R52" t="n">
-        <v>7264910</v>
+        <v>7264960</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775959</v>
+        <v>121775990</v>
       </c>
       <c r="B53" t="n">
-        <v>57373</v>
+        <v>78261</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751541</v>
+        <v>751420</v>
       </c>
       <c r="R53" t="n">
-        <v>7264963</v>
+        <v>7264903</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775978</v>
+        <v>121775966</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751407</v>
+        <v>751517</v>
       </c>
       <c r="R54" t="n">
         <v>7264897</v>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775983</v>
+        <v>121775975</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>90110</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6109,25 +6109,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751495</v>
+        <v>751479</v>
       </c>
       <c r="R55" t="n">
-        <v>7264900</v>
+        <v>7264948</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6167,12 +6167,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775975</v>
+        <v>121775974</v>
       </c>
       <c r="B56" t="n">
-        <v>90110</v>
+        <v>56561</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6211,25 +6211,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5685</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751479</v>
+        <v>751410</v>
       </c>
       <c r="R56" t="n">
-        <v>7264948</v>
+        <v>7264890</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775974</v>
+        <v>121775978</v>
       </c>
       <c r="B57" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751410</v>
+        <v>751407</v>
       </c>
       <c r="R57" t="n">
-        <v>7264890</v>
+        <v>7264897</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775963</v>
+        <v>121775983</v>
       </c>
       <c r="B47" t="n">
-        <v>78353</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751417</v>
+        <v>751495</v>
       </c>
       <c r="R47" t="n">
-        <v>7264910</v>
+        <v>7264900</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775959</v>
+        <v>121775974</v>
       </c>
       <c r="B48" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,16 +5399,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751541</v>
+        <v>751410</v>
       </c>
       <c r="R48" t="n">
-        <v>7264963</v>
+        <v>7264890</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775983</v>
+        <v>121775978</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751495</v>
+        <v>751407</v>
       </c>
       <c r="R49" t="n">
-        <v>7264900</v>
+        <v>7264897</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775977</v>
+        <v>121775975</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>90110</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5599,25 +5599,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751406</v>
+        <v>751479</v>
       </c>
       <c r="R50" t="n">
-        <v>7264892</v>
+        <v>7264948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775976</v>
+        <v>121775959</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751492</v>
+        <v>751541</v>
       </c>
       <c r="R52" t="n">
-        <v>7264960</v>
+        <v>7264963</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775990</v>
+        <v>121775966</v>
       </c>
       <c r="B53" t="n">
-        <v>78261</v>
+        <v>78352</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751420</v>
+        <v>751517</v>
       </c>
       <c r="R53" t="n">
-        <v>7264903</v>
+        <v>7264897</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775966</v>
+        <v>121775963</v>
       </c>
       <c r="B54" t="n">
-        <v>78352</v>
+        <v>78353</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,21 +6011,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751517</v>
+        <v>751417</v>
       </c>
       <c r="R54" t="n">
-        <v>7264897</v>
+        <v>7264910</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775975</v>
+        <v>121775976</v>
       </c>
       <c r="B55" t="n">
-        <v>90110</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6109,25 +6109,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751479</v>
+        <v>751492</v>
       </c>
       <c r="R55" t="n">
-        <v>7264948</v>
+        <v>7264960</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775974</v>
+        <v>121775990</v>
       </c>
       <c r="B56" t="n">
-        <v>56561</v>
+        <v>78261</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751410</v>
+        <v>751420</v>
       </c>
       <c r="R56" t="n">
-        <v>7264890</v>
+        <v>7264903</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775978</v>
+        <v>121775977</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751407</v>
+        <v>751406</v>
       </c>
       <c r="R57" t="n">
-        <v>7264897</v>
+        <v>7264892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775983</v>
+        <v>121775990</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>78261</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751495</v>
+        <v>751420</v>
       </c>
       <c r="R47" t="n">
-        <v>7264900</v>
+        <v>7264903</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775978</v>
+        <v>121775966</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751407</v>
+        <v>751517</v>
       </c>
       <c r="R49" t="n">
         <v>7264897</v>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775975</v>
+        <v>121775976</v>
       </c>
       <c r="B50" t="n">
-        <v>90110</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5599,25 +5599,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751479</v>
+        <v>751492</v>
       </c>
       <c r="R50" t="n">
-        <v>7264948</v>
+        <v>7264960</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775973</v>
+        <v>121775978</v>
       </c>
       <c r="B51" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,21 +5705,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751549</v>
+        <v>751407</v>
       </c>
       <c r="R51" t="n">
-        <v>7264968</v>
+        <v>7264897</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775959</v>
+        <v>121775963</v>
       </c>
       <c r="B52" t="n">
-        <v>57373</v>
+        <v>78353</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751541</v>
+        <v>751417</v>
       </c>
       <c r="R52" t="n">
-        <v>7264963</v>
+        <v>7264910</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775966</v>
+        <v>121775959</v>
       </c>
       <c r="B53" t="n">
-        <v>78352</v>
+        <v>57373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751517</v>
+        <v>751541</v>
       </c>
       <c r="R53" t="n">
-        <v>7264897</v>
+        <v>7264963</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775963</v>
+        <v>121775975</v>
       </c>
       <c r="B54" t="n">
-        <v>78353</v>
+        <v>90110</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6007,25 +6007,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>5685</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751417</v>
+        <v>751479</v>
       </c>
       <c r="R54" t="n">
-        <v>7264910</v>
+        <v>7264948</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775976</v>
+        <v>121775977</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751492</v>
+        <v>751406</v>
       </c>
       <c r="R55" t="n">
-        <v>7264960</v>
+        <v>7264892</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775990</v>
+        <v>121775973</v>
       </c>
       <c r="B56" t="n">
-        <v>78261</v>
+        <v>56561</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751420</v>
+        <v>751549</v>
       </c>
       <c r="R56" t="n">
-        <v>7264903</v>
+        <v>7264968</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775977</v>
+        <v>121775983</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751406</v>
+        <v>751495</v>
       </c>
       <c r="R57" t="n">
-        <v>7264892</v>
+        <v>7264900</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -5281,10 +5281,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775990</v>
+        <v>121775973</v>
       </c>
       <c r="B47" t="n">
-        <v>78261</v>
+        <v>56561</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751420</v>
+        <v>751549</v>
       </c>
       <c r="R47" t="n">
-        <v>7264903</v>
+        <v>7264968</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775974</v>
+        <v>121775976</v>
       </c>
       <c r="B48" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751410</v>
+        <v>751492</v>
       </c>
       <c r="R48" t="n">
-        <v>7264890</v>
+        <v>7264960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775976</v>
+        <v>121775974</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751492</v>
+        <v>751410</v>
       </c>
       <c r="R50" t="n">
-        <v>7264960</v>
+        <v>7264890</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775978</v>
+        <v>121775983</v>
       </c>
       <c r="B51" t="n">
         <v>78616</v>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751407</v>
+        <v>751495</v>
       </c>
       <c r="R51" t="n">
-        <v>7264897</v>
+        <v>7264900</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,12 +5759,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775963</v>
+        <v>121775990</v>
       </c>
       <c r="B52" t="n">
-        <v>78353</v>
+        <v>78261</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,21 +5807,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751417</v>
+        <v>751420</v>
       </c>
       <c r="R52" t="n">
-        <v>7264910</v>
+        <v>7264903</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775959</v>
+        <v>121775963</v>
       </c>
       <c r="B53" t="n">
-        <v>57373</v>
+        <v>78353</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751541</v>
+        <v>751417</v>
       </c>
       <c r="R53" t="n">
-        <v>7264963</v>
+        <v>7264910</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6199,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775973</v>
+        <v>121775978</v>
       </c>
       <c r="B56" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751549</v>
+        <v>751407</v>
       </c>
       <c r="R56" t="n">
-        <v>7264968</v>
+        <v>7264897</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775983</v>
+        <v>121775959</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6341,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751495</v>
+        <v>751541</v>
       </c>
       <c r="R57" t="n">
-        <v>7264900</v>
+        <v>7264963</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6527,6 +6527,2929 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127273305</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78678</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>353</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>751534</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7265195</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127273310</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>751722</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7265241</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127273294</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92802</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>751790</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7265146</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127273302</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91480</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>751604</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7265330</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127273307</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>751591</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7265038</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127273298</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>751712</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7265215</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127273286</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>751709</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7265163</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127273292</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>751718</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7265230</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127273291</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97320</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>751596</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7265044</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127273283</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>751713</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7265225</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127273290</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>751721</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7265253</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127273282</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>751666</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7265285</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127273309</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>751712</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7265138</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127273285</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>751714</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7265192</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127273303</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91480</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>751726</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7265134</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127273297</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>751706</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7265170</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127273306</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78678</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>353</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>751791</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7265139</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127273304</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91333</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>751715</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7265241</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127273288</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90354</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>751711</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7265216</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127273312</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78417</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>751748</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7265109</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127273314</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78417</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751709</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7265165</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127273308</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>751724</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7265132</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127273289</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91677</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>751712</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7265174</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127273301</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91940</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>751732</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7265129</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127273296</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>751710</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7265150</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127273300</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>751706</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7265203</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127273311</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92609</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>751722</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7265251</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127273295</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92802</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>751733</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7265129</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127273284</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91284</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>751598</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7265045</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127273299</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Björklidforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>751784</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7265143</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92609</v>
+        <v>92808</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92802</v>
+        <v>92615</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92609</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78770</v>
+        <v>92615</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79600</v>
+        <v>79038</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>79603</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91241</v>
+        <v>91247</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B69" t="n">
-        <v>57657</v>
+        <v>92615</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R69" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,11 +7570,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,7 +7599,7 @@
         <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>91241</v>
+        <v>91247</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7698,32 +7693,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>92609</v>
+        <v>57657</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,7 +7798,7 @@
         <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7892,48 +7892,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B73" t="n">
-        <v>91480</v>
+        <v>78773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7971,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,45 +7989,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B74" t="n">
-        <v>78770</v>
+        <v>91486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8072,6 +8071,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>91333</v>
+        <v>91339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>90354</v>
+        <v>90360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>127273312</v>
       </c>
       <c r="B78" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>127273314</v>
       </c>
       <c r="B79" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R83" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R84" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92808</v>
+        <v>92615</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R60" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92615</v>
+        <v>92808</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R61" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>92615</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7892,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>91486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7971,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7989,48 +7993,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B74" t="n">
-        <v>91486</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R74" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8071,7 +8072,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92808</v>
+        <v>91290</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91290</v>
+        <v>92808</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7570,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,32 +7601,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>91247</v>
+        <v>92615</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751712</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265138</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>57657</v>
+        <v>91247</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,45 +7795,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>91486</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R72" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,6 +7877,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7892,48 +7896,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B73" t="n">
-        <v>91486</v>
+        <v>78773</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7975,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>127273304</v>
       </c>
       <c r="B75" t="n">
-        <v>78681</v>
+        <v>91339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,34 +8101,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751715</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7265241</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8169,6 +8172,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8187,10 +8191,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>127273288</v>
       </c>
       <c r="B76" t="n">
-        <v>91339</v>
+        <v>90360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,37 +8202,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751711</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7265216</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8269,7 +8270,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B77" t="n">
-        <v>90360</v>
+        <v>78681</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92615</v>
+        <v>92809</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92808</v>
+        <v>92616</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79038</v>
+        <v>79603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79603</v>
+        <v>79038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,48 +7795,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>91486</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7877,7 +7874,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7896,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>78773</v>
+        <v>91487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7975,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273304</v>
+        <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>91339</v>
+        <v>78681</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,37 +8101,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751715</v>
+        <v>751791</v>
       </c>
       <c r="R75" t="n">
-        <v>7265241</v>
+        <v>7265139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8172,7 +8169,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8191,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>90360</v>
+        <v>91340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8202,34 +8198,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R76" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8270,6 +8269,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>78681</v>
+        <v>90361</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91946</v>
+        <v>91947</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91290</v>
+        <v>92809</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92808</v>
+        <v>91291</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79603</v>
+        <v>79038</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79038</v>
+        <v>79603</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B74" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R60" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R61" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91684</v>
+        <v>91947</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R81" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91947</v>
+        <v>91684</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R82" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92809</v>
+        <v>91291</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91291</v>
+        <v>92809</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79038</v>
+        <v>79603</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79603</v>
+        <v>79038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7795,45 +7795,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,6 +7877,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7892,48 +7896,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B73" t="n">
-        <v>91487</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7975,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79603</v>
+        <v>79038</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79038</v>
+        <v>79603</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7795,48 +7795,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>91487</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7877,7 +7874,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7896,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7975,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6406,7 +6406,7 @@
         <v>127059027</v>
       </c>
       <c r="B58" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79038</v>
+        <v>79607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79603</v>
+        <v>79042</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B69" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R69" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,11 +7570,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7601,32 +7596,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273309</v>
+        <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>92616</v>
+        <v>91252</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751712</v>
+        <v>751666</v>
       </c>
       <c r="R70" t="n">
-        <v>7265138</v>
+        <v>7265285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>91248</v>
+        <v>57661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,7 +7798,7 @@
         <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>90361</v>
+        <v>90365</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>127273312</v>
       </c>
       <c r="B78" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>127273314</v>
       </c>
       <c r="B79" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91947</v>
+        <v>91688</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R81" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91684</v>
+        <v>91951</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R82" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8873,7 +8873,7 @@
         <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91291</v>
+        <v>92813</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92809</v>
+        <v>91295</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>79042</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79042</v>
+        <v>79607</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7596,10 +7596,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B70" t="n">
-        <v>91252</v>
+        <v>57661</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,6 +7667,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7693,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>57661</v>
+        <v>91252</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,45 +7795,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>91491</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,6 +7877,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7892,48 +7896,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B73" t="n">
-        <v>91491</v>
+        <v>78777</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7975,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B75" t="n">
-        <v>78685</v>
+        <v>90365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>127273306</v>
       </c>
       <c r="B76" t="n">
-        <v>91344</v>
+        <v>78685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,37 +8198,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751791</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7265139</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8269,7 +8266,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8284,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B77" t="n">
-        <v>90365</v>
+        <v>91344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,34 +8295,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8367,6 +8366,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>90365</v>
+        <v>78685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R75" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273306</v>
+        <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>78685</v>
+        <v>91344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,34 +8198,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751791</v>
+        <v>751715</v>
       </c>
       <c r="R76" t="n">
-        <v>7265139</v>
+        <v>7265241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8266,6 +8269,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8284,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273304</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>91344</v>
+        <v>90365</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8295,37 +8299,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751715</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265241</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8366,7 +8367,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92620</v>
+        <v>78777</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B73" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7931,10 +7931,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R73" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B75" t="n">
-        <v>78685</v>
+        <v>90365</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>127273306</v>
       </c>
       <c r="B76" t="n">
-        <v>91344</v>
+        <v>78685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,37 +8198,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751791</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7265139</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8269,7 +8266,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8284,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B77" t="n">
-        <v>90365</v>
+        <v>91344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,34 +8295,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8367,6 +8366,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92813</v>
+        <v>92620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R60" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92620</v>
+        <v>92813</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R61" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79042</v>
+        <v>79607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>79042</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7596,10 +7596,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>91252</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R70" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,11 +7667,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7698,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>91252</v>
+        <v>57661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,48 +7795,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7877,7 +7874,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7896,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>79636</v>
+        <v>91491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7975,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273306</v>
+        <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>78685</v>
+        <v>91344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,34 +8198,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751791</v>
+        <v>751715</v>
       </c>
       <c r="R76" t="n">
-        <v>7265139</v>
+        <v>7265241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8266,6 +8269,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8284,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273304</v>
+        <v>127273306</v>
       </c>
       <c r="B77" t="n">
-        <v>91344</v>
+        <v>78685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8295,37 +8299,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751715</v>
+        <v>751791</v>
       </c>
       <c r="R77" t="n">
-        <v>7265241</v>
+        <v>7265139</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8366,7 +8367,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91688</v>
+        <v>91951</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R81" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91951</v>
+        <v>91688</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R82" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92813</v>
+        <v>91295</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91295</v>
+        <v>92813</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7892,48 +7892,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B73" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7971,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,45 +7989,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>91491</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8072,6 +8071,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6406,7 +6406,7 @@
         <v>127059027</v>
       </c>
       <c r="B58" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7570,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,32 +7601,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>91252</v>
+        <v>92622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751712</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265138</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>57661</v>
+        <v>91254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7892,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>79636</v>
+        <v>91493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7971,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7989,48 +7993,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>91491</v>
+        <v>78779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8071,7 +8072,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>90365</v>
+        <v>78687</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R75" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8190,7 +8190,7 @@
         <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>91344</v>
+        <v>91346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>78685</v>
+        <v>90367</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,10 +8385,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127273312</v>
+        <v>127273314</v>
       </c>
       <c r="B78" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751748</v>
+        <v>751709</v>
       </c>
       <c r="R78" t="n">
-        <v>7265109</v>
+        <v>7265165</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127273314</v>
+        <v>127273312</v>
       </c>
       <c r="B79" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>751709</v>
+        <v>751748</v>
       </c>
       <c r="R79" t="n">
-        <v>7265165</v>
+        <v>7265109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91951</v>
+        <v>91690</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R81" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91688</v>
+        <v>91953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R82" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8873,7 +8873,7 @@
         <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91295</v>
+        <v>92815</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92813</v>
+        <v>91297</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B69" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R69" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,11 +7570,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7601,32 +7596,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273309</v>
+        <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>92622</v>
+        <v>91254</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751712</v>
+        <v>751666</v>
       </c>
       <c r="R70" t="n">
-        <v>7265138</v>
+        <v>7265285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>91254</v>
+        <v>57663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B72" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273285</v>
       </c>
       <c r="B74" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751714</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265192</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>127273288</v>
       </c>
       <c r="B76" t="n">
-        <v>91346</v>
+        <v>90367</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,37 +8198,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751711</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7265216</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8269,7 +8266,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8284,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B77" t="n">
-        <v>90367</v>
+        <v>91346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,34 +8295,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8367,6 +8366,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91690</v>
+        <v>91953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R81" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91953</v>
+        <v>91690</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R82" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92815</v>
+        <v>91297</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91297</v>
+        <v>92815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R60" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R61" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B83" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R83" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B84" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R84" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91297</v>
+        <v>92815</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92815</v>
+        <v>91297</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92622</v>
+        <v>92815</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79609</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7570,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,32 +7601,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>91254</v>
+        <v>92622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751712</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265138</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>57663</v>
+        <v>91254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,45 +7795,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B72" t="n">
-        <v>78779</v>
+        <v>91493</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R72" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7874,6 +7877,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7892,48 +7896,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B73" t="n">
-        <v>91493</v>
+        <v>79638</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7975,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,10 +7993,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273285</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8004,21 +8004,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751714</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265192</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8187,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>90367</v>
+        <v>91346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,34 +8198,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R76" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8266,6 +8269,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8284,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273304</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>91346</v>
+        <v>90367</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8295,37 +8299,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751715</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265241</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8366,7 +8367,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127273314</v>
+        <v>127273312</v>
       </c>
       <c r="B78" t="n">
         <v>78426</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751709</v>
+        <v>751748</v>
       </c>
       <c r="R78" t="n">
-        <v>7265165</v>
+        <v>7265109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,7 +8482,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127273312</v>
+        <v>127273314</v>
       </c>
       <c r="B79" t="n">
         <v>78426</v>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>751748</v>
+        <v>751709</v>
       </c>
       <c r="R79" t="n">
-        <v>7265109</v>
+        <v>7265165</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R83" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R84" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92815</v>
+        <v>91297</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91297</v>
+        <v>92815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6629,7 +6629,7 @@
         <v>127273294</v>
       </c>
       <c r="B60" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273310</v>
       </c>
       <c r="B61" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78779</v>
+        <v>92628</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79609</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79609</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91254</v>
+        <v>91260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>91254</v>
+        <v>91260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7795,48 +7795,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273303</v>
+        <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>91493</v>
+        <v>79638</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751726</v>
+        <v>751714</v>
       </c>
       <c r="R72" t="n">
-        <v>7265134</v>
+        <v>7265192</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7877,7 +7874,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7896,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273285</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>79638</v>
+        <v>91499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751714</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265192</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7975,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>127273304</v>
       </c>
       <c r="B75" t="n">
-        <v>78687</v>
+        <v>91352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,34 +8101,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751715</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7265241</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8169,6 +8172,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8187,10 +8191,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>127273288</v>
       </c>
       <c r="B76" t="n">
-        <v>91346</v>
+        <v>90373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8198,37 +8202,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751711</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7265216</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8269,7 +8270,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B77" t="n">
-        <v>90367</v>
+        <v>78687</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91953</v>
+        <v>91696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R81" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91690</v>
+        <v>91959</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R82" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91297</v>
+        <v>92821</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92815</v>
+        <v>91303</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6626,32 +6626,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273294</v>
+        <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92821</v>
+        <v>92631</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751790</v>
+        <v>751722</v>
       </c>
       <c r="R60" t="n">
-        <v>7265146</v>
+        <v>7265241</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,32 +6723,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273310</v>
+        <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92628</v>
+        <v>92824</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751722</v>
+        <v>751790</v>
       </c>
       <c r="R61" t="n">
-        <v>7265241</v>
+        <v>7265146</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78779</v>
+        <v>92631</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92628</v>
+        <v>78782</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7114,7 +7114,7 @@
         <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>127273304</v>
       </c>
       <c r="B75" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>127273288</v>
       </c>
       <c r="B76" t="n">
-        <v>90373</v>
+        <v>90376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127273306</v>
       </c>
       <c r="B77" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>127273312</v>
       </c>
       <c r="B78" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>127273314</v>
       </c>
       <c r="B79" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91696</v>
+        <v>91962</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R81" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91959</v>
+        <v>91699</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R82" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8873,7 +8873,7 @@
         <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B65" t="n">
-        <v>79612</v>
+        <v>79053</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R65" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B66" t="n">
-        <v>79047</v>
+        <v>79618</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R66" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91263</v>
+        <v>91271</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B69" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R69" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,11 +7570,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7601,32 +7596,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273309</v>
+        <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>92631</v>
+        <v>91271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751712</v>
+        <v>751666</v>
       </c>
       <c r="R70" t="n">
-        <v>7265138</v>
+        <v>7265285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>91263</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,7 +7798,7 @@
         <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273304</v>
+        <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>91355</v>
+        <v>78696</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,37 +8101,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751715</v>
+        <v>751791</v>
       </c>
       <c r="R75" t="n">
-        <v>7265241</v>
+        <v>7265139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8172,7 +8169,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8191,10 +8187,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273288</v>
+        <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>90376</v>
+        <v>91363</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8202,34 +8198,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751711</v>
+        <v>751715</v>
       </c>
       <c r="R76" t="n">
-        <v>7265216</v>
+        <v>7265241</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8270,6 +8269,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>78690</v>
+        <v>90384</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,10 +8385,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127273312</v>
+        <v>127273314</v>
       </c>
       <c r="B78" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751748</v>
+        <v>751709</v>
       </c>
       <c r="R78" t="n">
-        <v>7265109</v>
+        <v>7265165</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127273314</v>
+        <v>127273312</v>
       </c>
       <c r="B79" t="n">
-        <v>78429</v>
+        <v>78435</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>751709</v>
+        <v>751748</v>
       </c>
       <c r="R79" t="n">
-        <v>7265165</v>
+        <v>7265109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91962</v>
+        <v>91970</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B83" t="n">
-        <v>78781</v>
+        <v>78788</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R83" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B84" t="n">
-        <v>78782</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R84" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6629,7 +6629,7 @@
         <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B63" t="n">
-        <v>92639</v>
+        <v>78788</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>92640</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7570,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,32 +7601,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273309</v>
       </c>
       <c r="B70" t="n">
-        <v>91271</v>
+        <v>92640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7636,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751712</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265138</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273282</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>91272</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751666</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265285</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7892,48 +7892,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B73" t="n">
-        <v>91510</v>
+        <v>78788</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7974,7 +7971,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,45 +7989,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>91511</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8072,6 +8071,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B75" t="n">
-        <v>78696</v>
+        <v>90385</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8190,7 +8190,7 @@
         <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B77" t="n">
-        <v>90384</v>
+        <v>78696</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127273314</v>
+        <v>127273312</v>
       </c>
       <c r="B78" t="n">
         <v>78435</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751709</v>
+        <v>751748</v>
       </c>
       <c r="R78" t="n">
-        <v>7265165</v>
+        <v>7265109</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,7 +8482,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127273312</v>
+        <v>127273314</v>
       </c>
       <c r="B79" t="n">
         <v>78435</v>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>751748</v>
+        <v>751709</v>
       </c>
       <c r="R79" t="n">
-        <v>7265109</v>
+        <v>7265165</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>127273301</v>
       </c>
       <c r="B81" t="n">
-        <v>91970</v>
+        <v>91971</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127273289</v>
       </c>
       <c r="B82" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B86" t="n">
-        <v>92832</v>
+        <v>91315</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R86" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B87" t="n">
-        <v>91314</v>
+        <v>92833</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R87" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6917,32 +6917,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273298</v>
+        <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>92640</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751712</v>
+        <v>751591</v>
       </c>
       <c r="R63" t="n">
-        <v>7265215</v>
+        <v>7265038</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7014,32 +7014,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273307</v>
+        <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>92640</v>
+        <v>78788</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751591</v>
+        <v>751712</v>
       </c>
       <c r="R64" t="n">
-        <v>7265038</v>
+        <v>7265215</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B69" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R69" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,11 +7570,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7601,32 +7596,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273309</v>
+        <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>92640</v>
+        <v>91272</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7636,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751712</v>
+        <v>751666</v>
       </c>
       <c r="R70" t="n">
-        <v>7265138</v>
+        <v>7265285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7698,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273282</v>
+        <v>127273290</v>
       </c>
       <c r="B71" t="n">
-        <v>91272</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,21 +7704,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751666</v>
+        <v>751721</v>
       </c>
       <c r="R71" t="n">
-        <v>7265285</v>
+        <v>7265253</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,6 +7764,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7892,45 +7892,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273297</v>
+        <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>91511</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751706</v>
+        <v>751726</v>
       </c>
       <c r="R73" t="n">
-        <v>7265170</v>
+        <v>7265134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7971,6 +7974,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7989,48 +7993,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273303</v>
+        <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>91511</v>
+        <v>78788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751726</v>
+        <v>751706</v>
       </c>
       <c r="R74" t="n">
-        <v>7265134</v>
+        <v>7265170</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8071,7 +8072,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8090,10 +8090,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273288</v>
+        <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>90385</v>
+        <v>78696</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8101,21 +8101,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8125,10 +8125,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751711</v>
+        <v>751791</v>
       </c>
       <c r="R75" t="n">
-        <v>7265216</v>
+        <v>7265139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273306</v>
+        <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>78696</v>
+        <v>90385</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751791</v>
+        <v>751711</v>
       </c>
       <c r="R77" t="n">
-        <v>7265139</v>
+        <v>7265216</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8676,32 +8676,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273301</v>
+        <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91971</v>
+        <v>91708</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5454</v>
+        <v>2062</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751732</v>
+        <v>751712</v>
       </c>
       <c r="R81" t="n">
-        <v>7265129</v>
+        <v>7265174</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8773,32 +8773,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273289</v>
+        <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91708</v>
+        <v>91971</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>5454</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751712</v>
+        <v>751732</v>
       </c>
       <c r="R82" t="n">
-        <v>7265174</v>
+        <v>7265129</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B83" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R83" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R84" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -6406,7 +6406,7 @@
         <v>127059027</v>
       </c>
       <c r="B58" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>127273305</v>
       </c>
       <c r="B59" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>127273310</v>
       </c>
       <c r="B60" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127273294</v>
       </c>
       <c r="B61" t="n">
-        <v>92833</v>
+        <v>92802</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127273302</v>
       </c>
       <c r="B62" t="n">
-        <v>91511</v>
+        <v>91480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127273307</v>
       </c>
       <c r="B63" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127273298</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7111,32 +7111,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>127273286</v>
       </c>
       <c r="B65" t="n">
-        <v>79053</v>
+        <v>79600</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751709</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265163</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,32 +7208,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>127273292</v>
       </c>
       <c r="B66" t="n">
-        <v>79618</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751718</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7265230</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>127273291</v>
       </c>
       <c r="B67" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>127273283</v>
       </c>
       <c r="B68" t="n">
-        <v>91272</v>
+        <v>91241</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7499,32 +7499,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>127273290</v>
       </c>
       <c r="B69" t="n">
-        <v>92640</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751721</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265253</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7570,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7599,7 +7604,7 @@
         <v>127273282</v>
       </c>
       <c r="B70" t="n">
-        <v>91272</v>
+        <v>91241</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7693,32 +7698,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>127273309</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>92609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751712</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7265138</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,11 +7769,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7798,7 +7798,7 @@
         <v>127273285</v>
       </c>
       <c r="B72" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>127273303</v>
       </c>
       <c r="B73" t="n">
-        <v>91511</v>
+        <v>91480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>127273297</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>127273306</v>
       </c>
       <c r="B75" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>127273304</v>
       </c>
       <c r="B76" t="n">
-        <v>91364</v>
+        <v>91333</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127273288</v>
       </c>
       <c r="B77" t="n">
-        <v>90385</v>
+        <v>90354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>127273312</v>
       </c>
       <c r="B78" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>127273314</v>
       </c>
       <c r="B79" t="n">
-        <v>78435</v>
+        <v>78417</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>127273308</v>
       </c>
       <c r="B80" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>127273289</v>
       </c>
       <c r="B81" t="n">
-        <v>91708</v>
+        <v>91677</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>127273301</v>
       </c>
       <c r="B82" t="n">
-        <v>91971</v>
+        <v>91940</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273300</v>
+        <v>127273296</v>
       </c>
       <c r="B83" t="n">
-        <v>78787</v>
+        <v>78770</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,21 +8881,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751706</v>
+        <v>751710</v>
       </c>
       <c r="R83" t="n">
-        <v>7265203</v>
+        <v>7265150</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8967,10 +8967,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127273296</v>
+        <v>127273300</v>
       </c>
       <c r="B84" t="n">
-        <v>78788</v>
+        <v>78769</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>751710</v>
+        <v>751706</v>
       </c>
       <c r="R84" t="n">
-        <v>7265150</v>
+        <v>7265203</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9067,7 +9067,7 @@
         <v>127273311</v>
       </c>
       <c r="B85" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9161,32 +9161,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273295</v>
       </c>
       <c r="B86" t="n">
-        <v>91315</v>
+        <v>92802</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751733</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265129</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,32 +9258,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>127273284</v>
       </c>
       <c r="B87" t="n">
-        <v>92833</v>
+        <v>91284</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751598</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265045</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
         <v>127273299</v>
       </c>
       <c r="B88" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120707839</v>
+        <v>120707853</v>
       </c>
       <c r="B2" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751619</v>
+        <v>751538</v>
       </c>
       <c r="R2" t="n">
-        <v>7265267</v>
+        <v>7265173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120707840</v>
+        <v>120707854</v>
       </c>
       <c r="B3" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751630</v>
+        <v>751614</v>
       </c>
       <c r="R3" t="n">
-        <v>7265346</v>
+        <v>7265293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120707853</v>
+        <v>120707855</v>
       </c>
       <c r="B4" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751538</v>
+        <v>751615</v>
       </c>
       <c r="R4" t="n">
-        <v>7265173</v>
+        <v>7265332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120707820</v>
+        <v>120707856</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751607</v>
+        <v>751664</v>
       </c>
       <c r="R5" t="n">
-        <v>7265329</v>
+        <v>7265370</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,66 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120707824</v>
+        <v>120707857</v>
       </c>
       <c r="B6" t="n">
-        <v>56560</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751695</v>
+        <v>751660</v>
       </c>
       <c r="R6" t="n">
-        <v>7265275</v>
+        <v>7265319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120707843</v>
+        <v>120707858</v>
       </c>
       <c r="B7" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751678</v>
+        <v>751681</v>
       </c>
       <c r="R7" t="n">
-        <v>7265289</v>
+        <v>7265284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120707841</v>
+        <v>121775990</v>
       </c>
       <c r="B8" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751608</v>
+        <v>751420</v>
       </c>
       <c r="R8" t="n">
-        <v>7265248</v>
+        <v>7264903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120707860</v>
+        <v>127273305</v>
       </c>
       <c r="B9" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751611</v>
+        <v>751534</v>
       </c>
       <c r="R9" t="n">
-        <v>7265303</v>
+        <v>7265195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120707861</v>
+        <v>127273306</v>
       </c>
       <c r="B10" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751604</v>
+        <v>751791</v>
       </c>
       <c r="R10" t="n">
-        <v>7265332</v>
+        <v>7265139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120707827</v>
+        <v>121775967</v>
       </c>
       <c r="B11" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751677</v>
+        <v>751404</v>
       </c>
       <c r="R11" t="n">
-        <v>7265294</v>
+        <v>7264874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,50 +1645,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120707829</v>
+        <v>127273304</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4745</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751662</v>
+        <v>751715</v>
       </c>
       <c r="R12" t="n">
-        <v>7265362</v>
+        <v>7265241</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,12 +1713,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,6 +1727,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1813,37 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120707821</v>
+        <v>120760993</v>
       </c>
       <c r="B13" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751597</v>
+        <v>751523</v>
       </c>
       <c r="R13" t="n">
-        <v>7265327</v>
+        <v>7265203</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,37 +1843,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120707834</v>
+        <v>127273302</v>
       </c>
       <c r="B14" t="n">
-        <v>91971</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751610</v>
+        <v>751604</v>
       </c>
       <c r="R14" t="n">
-        <v>7265259</v>
+        <v>7265330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,12 +1908,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,50 +1940,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120707844</v>
+        <v>127273303</v>
       </c>
       <c r="B15" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751545</v>
+        <v>751726</v>
       </c>
       <c r="R15" t="n">
-        <v>7265176</v>
+        <v>7265134</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,12 +2008,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,6 +2022,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2119,37 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120707867</v>
+        <v>120707821</v>
       </c>
       <c r="B16" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751680</v>
+        <v>751597</v>
       </c>
       <c r="R16" t="n">
-        <v>7265284</v>
+        <v>7265327</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,37 +2138,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120707865</v>
+        <v>120707822</v>
       </c>
       <c r="B17" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751625</v>
+        <v>751641</v>
       </c>
       <c r="R17" t="n">
-        <v>7265377</v>
+        <v>7265383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,37 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120707862</v>
+        <v>127273288</v>
       </c>
       <c r="B18" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751607</v>
+        <v>751711</v>
       </c>
       <c r="R18" t="n">
-        <v>7265332</v>
+        <v>7265216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,12 +2300,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2425,37 +2332,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120707833</v>
+        <v>120707834</v>
       </c>
       <c r="B19" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751637</v>
+        <v>751610</v>
       </c>
       <c r="R19" t="n">
-        <v>7265400</v>
+        <v>7265259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,37 +2429,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120707859</v>
+        <v>120707835</v>
       </c>
       <c r="B20" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2464,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751556</v>
+        <v>751596</v>
       </c>
       <c r="R20" t="n">
-        <v>7265220</v>
+        <v>7265321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,37 +2526,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120707866</v>
+        <v>120707836</v>
       </c>
       <c r="B21" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2561,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751652</v>
+        <v>751643</v>
       </c>
       <c r="R21" t="n">
-        <v>7265349</v>
+        <v>7265358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2731,37 +2623,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120707858</v>
+        <v>127273289</v>
       </c>
       <c r="B22" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2658,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751681</v>
+        <v>751712</v>
       </c>
       <c r="R22" t="n">
-        <v>7265284</v>
+        <v>7265174</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,12 +2688,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2833,15 +2720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120707846</v>
+        <v>127273294</v>
       </c>
       <c r="B23" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,21 +2731,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2755,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751608</v>
+        <v>751790</v>
       </c>
       <c r="R23" t="n">
-        <v>7265298</v>
+        <v>7265146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,12 +2785,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2935,37 +2817,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120707863</v>
+        <v>127273295</v>
       </c>
       <c r="B24" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2975,10 +2852,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751626</v>
+        <v>751733</v>
       </c>
       <c r="R24" t="n">
-        <v>7265341</v>
+        <v>7265129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,12 +2882,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,37 +2914,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120707864</v>
+        <v>127273282</v>
       </c>
       <c r="B25" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +2949,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751638</v>
+        <v>751666</v>
       </c>
       <c r="R25" t="n">
-        <v>7265365</v>
+        <v>7265285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,12 +2979,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,15 +3011,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120707830</v>
+        <v>127273283</v>
       </c>
       <c r="B26" t="n">
-        <v>91581</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,21 +3022,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>3242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3046,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751679</v>
+        <v>751713</v>
       </c>
       <c r="R26" t="n">
-        <v>7265285</v>
+        <v>7265225</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,12 +3076,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3241,15 +3108,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120707835</v>
+        <v>120707839</v>
       </c>
       <c r="B27" t="n">
-        <v>91971</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,21 +3119,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3143,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751596</v>
+        <v>751619</v>
       </c>
       <c r="R27" t="n">
-        <v>7265321</v>
+        <v>7265267</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,15 +3205,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120707869</v>
+        <v>120707840</v>
       </c>
       <c r="B28" t="n">
-        <v>77978</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,21 +3216,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3240,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751668</v>
+        <v>751630</v>
       </c>
       <c r="R28" t="n">
-        <v>7265309</v>
+        <v>7265346</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3445,37 +3302,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120707818</v>
+        <v>120707859</v>
       </c>
       <c r="B29" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3337,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>751641</v>
+        <v>751556</v>
       </c>
       <c r="R29" t="n">
-        <v>7265382</v>
+        <v>7265220</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3547,15 +3399,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120707828</v>
+        <v>120707860</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3563,21 +3410,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3434,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751541</v>
+        <v>751611</v>
       </c>
       <c r="R30" t="n">
-        <v>7265178</v>
+        <v>7265303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,15 +3496,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120707836</v>
+        <v>120707861</v>
       </c>
       <c r="B31" t="n">
-        <v>91971</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,21 +3507,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3531,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751643</v>
+        <v>751604</v>
       </c>
       <c r="R31" t="n">
-        <v>7265358</v>
+        <v>7265332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,15 +3593,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120707822</v>
+        <v>120707862</v>
       </c>
       <c r="B32" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,21 +3604,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3628,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751641</v>
+        <v>751607</v>
       </c>
       <c r="R32" t="n">
-        <v>7265383</v>
+        <v>7265332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3853,15 +3690,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120707847</v>
+        <v>120707863</v>
       </c>
       <c r="B33" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3869,21 +3701,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3725,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751658</v>
+        <v>751626</v>
       </c>
       <c r="R33" t="n">
-        <v>7265332</v>
+        <v>7265341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3955,15 +3787,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120707845</v>
+        <v>120707864</v>
       </c>
       <c r="B34" t="n">
-        <v>78330</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3971,21 +3798,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3822,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751561</v>
+        <v>751638</v>
       </c>
       <c r="R34" t="n">
-        <v>7265244</v>
+        <v>7265365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4057,15 +3884,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120707857</v>
+        <v>120707865</v>
       </c>
       <c r="B35" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,21 +3895,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +3919,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751660</v>
+        <v>751625</v>
       </c>
       <c r="R35" t="n">
-        <v>7265319</v>
+        <v>7265377</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,15 +3981,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120707855</v>
+        <v>120707866</v>
       </c>
       <c r="B36" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4175,21 +3992,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4016,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751615</v>
+        <v>751652</v>
       </c>
       <c r="R36" t="n">
-        <v>7265332</v>
+        <v>7265349</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,15 +4078,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120707851</v>
+        <v>120707867</v>
       </c>
       <c r="B37" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4277,21 +4089,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4301,10 +4113,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751616</v>
+        <v>751680</v>
       </c>
       <c r="R37" t="n">
-        <v>7265258</v>
+        <v>7265284</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,15 +4175,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120707831</v>
+        <v>127273307</v>
       </c>
       <c r="B38" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,21 +4186,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4403,10 +4210,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751610</v>
+        <v>751591</v>
       </c>
       <c r="R38" t="n">
-        <v>7265305</v>
+        <v>7265038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4433,12 +4240,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4465,37 +4272,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120707817</v>
+        <v>127273308</v>
       </c>
       <c r="B39" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4307,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751605</v>
+        <v>751724</v>
       </c>
       <c r="R39" t="n">
-        <v>7265337</v>
+        <v>7265132</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4535,12 +4337,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4567,15 +4369,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120707852</v>
+        <v>127273309</v>
       </c>
       <c r="B40" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4583,21 +4380,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4607,10 +4404,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751655</v>
+        <v>751712</v>
       </c>
       <c r="R40" t="n">
-        <v>7265309</v>
+        <v>7265138</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,12 +4434,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4669,15 +4466,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120707819</v>
+        <v>127273310</v>
       </c>
       <c r="B41" t="n">
-        <v>79212</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4685,21 +4477,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4709,10 +4501,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751541</v>
+        <v>751722</v>
       </c>
       <c r="R41" t="n">
-        <v>7265181</v>
+        <v>7265241</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,12 +4531,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4771,15 +4563,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120707856</v>
+        <v>127273311</v>
       </c>
       <c r="B42" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4787,21 +4574,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4811,10 +4598,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751664</v>
+        <v>751722</v>
       </c>
       <c r="R42" t="n">
-        <v>7265370</v>
+        <v>7265251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4841,12 +4628,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4873,15 +4660,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120707842</v>
+        <v>120707828</v>
       </c>
       <c r="B43" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,21 +4671,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4913,10 +4695,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751574</v>
+        <v>751541</v>
       </c>
       <c r="R43" t="n">
-        <v>7265243</v>
+        <v>7265178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4975,15 +4757,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120707854</v>
+        <v>120707829</v>
       </c>
       <c r="B44" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4991,21 +4768,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5015,10 +4792,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751614</v>
+        <v>751662</v>
       </c>
       <c r="R44" t="n">
-        <v>7265293</v>
+        <v>7265362</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5077,15 +4854,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120707832</v>
+        <v>120707830</v>
       </c>
       <c r="B45" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,21 +4865,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5117,10 +4889,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751636</v>
+        <v>751679</v>
       </c>
       <c r="R45" t="n">
-        <v>7265382</v>
+        <v>7265285</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5179,37 +4951,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120760993</v>
+        <v>120707817</v>
       </c>
       <c r="B46" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5219,10 +4986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751523</v>
+        <v>751605</v>
       </c>
       <c r="R46" t="n">
-        <v>7265203</v>
+        <v>7265337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5281,50 +5048,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121775976</v>
+        <v>120707818</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Björkliden-Åbyälven, Nb</t>
+          <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751492</v>
+        <v>751641</v>
       </c>
       <c r="R47" t="n">
-        <v>7264960</v>
+        <v>7265382</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,12 +5113,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5383,50 +5145,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121775973</v>
+        <v>127273284</v>
       </c>
       <c r="B48" t="n">
-        <v>56576</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björkliden-Åbyälven, Nb</t>
+          <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751549</v>
+        <v>751598</v>
       </c>
       <c r="R48" t="n">
-        <v>7264968</v>
+        <v>7265045</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,12 +5210,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,15 +5242,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121775990</v>
+        <v>127273301</v>
       </c>
       <c r="B49" t="n">
-        <v>78290</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5501,34 +5253,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>5454</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björkliden-Åbyälven, Nb</t>
+          <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751420</v>
+        <v>751732</v>
       </c>
       <c r="R49" t="n">
-        <v>7264903</v>
+        <v>7265129</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,12 +5307,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,37 +5339,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121775978</v>
+        <v>121775975</v>
       </c>
       <c r="B50" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5374,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751407</v>
+        <v>751479</v>
       </c>
       <c r="R50" t="n">
-        <v>7264897</v>
+        <v>7264948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,50 +5436,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121775975</v>
+        <v>120707851</v>
       </c>
       <c r="B51" t="n">
-        <v>90145</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björkliden-Åbyälven, Nb</t>
+          <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751479</v>
+        <v>751616</v>
       </c>
       <c r="R51" t="n">
-        <v>7264948</v>
+        <v>7265258</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,12 +5501,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5791,50 +5533,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121775966</v>
+        <v>120707852</v>
       </c>
       <c r="B52" t="n">
-        <v>78381</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Björkliden-Åbyälven, Nb</t>
+          <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751517</v>
+        <v>751655</v>
       </c>
       <c r="R52" t="n">
-        <v>7264897</v>
+        <v>7265309</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5861,12 +5598,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5893,37 +5630,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121775963</v>
+        <v>121775976</v>
       </c>
       <c r="B53" t="n">
-        <v>78382</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5933,10 +5665,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751417</v>
+        <v>751492</v>
       </c>
       <c r="R53" t="n">
-        <v>7264910</v>
+        <v>7264960</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5995,37 +5727,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121775959</v>
+        <v>121775977</v>
       </c>
       <c r="B54" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6035,10 +5762,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751541</v>
+        <v>751406</v>
       </c>
       <c r="R54" t="n">
-        <v>7264963</v>
+        <v>7264892</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6097,19 +5824,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121775983</v>
+        <v>121775978</v>
       </c>
       <c r="B55" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6137,10 +5859,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751495</v>
+        <v>751407</v>
       </c>
       <c r="R55" t="n">
-        <v>7264900</v>
+        <v>7264897</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6167,12 +5889,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6199,19 +5921,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121775977</v>
+        <v>121775979</v>
       </c>
       <c r="B56" t="n">
-        <v>78645</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6239,10 +5956,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751406</v>
+        <v>751401</v>
       </c>
       <c r="R56" t="n">
-        <v>7264892</v>
+        <v>7264879</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,37 +6018,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121775974</v>
+        <v>121775983</v>
       </c>
       <c r="B57" t="n">
-        <v>56576</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6341,10 +6053,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751410</v>
+        <v>751495</v>
       </c>
       <c r="R57" t="n">
-        <v>7264890</v>
+        <v>7264900</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,12 +6083,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6403,10 +6115,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127059027</v>
+        <v>127273292</v>
       </c>
       <c r="B58" t="n">
-        <v>56855</v>
+        <v>79351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6414,53 +6126,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>751658</v>
+        <v>751718</v>
       </c>
       <c r="R58" t="n">
-        <v>7265261</v>
+        <v>7265230</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6487,22 +6180,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>20:40</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6529,10 +6212,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127273305</v>
+        <v>120707869</v>
       </c>
       <c r="B59" t="n">
-        <v>78696</v>
+        <v>78730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6540,21 +6223,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6564,10 +6247,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>751534</v>
+        <v>751668</v>
       </c>
       <c r="R59" t="n">
-        <v>7265195</v>
+        <v>7265309</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6594,12 +6277,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6626,32 +6309,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127273310</v>
+        <v>127273312</v>
       </c>
       <c r="B60" t="n">
-        <v>92640</v>
+        <v>78730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6661,10 +6344,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751722</v>
+        <v>751748</v>
       </c>
       <c r="R60" t="n">
-        <v>7265241</v>
+        <v>7265109</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6723,10 +6406,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127273294</v>
+        <v>127273314</v>
       </c>
       <c r="B61" t="n">
-        <v>92833</v>
+        <v>78730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6734,21 +6417,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,10 +6441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751790</v>
+        <v>751709</v>
       </c>
       <c r="R61" t="n">
-        <v>7265146</v>
+        <v>7265165</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6820,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127273302</v>
+        <v>120707844</v>
       </c>
       <c r="B62" t="n">
-        <v>91511</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>751604</v>
+        <v>751545</v>
       </c>
       <c r="R62" t="n">
-        <v>7265330</v>
+        <v>7265176</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6885,12 +6568,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6917,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127273307</v>
+        <v>120707845</v>
       </c>
       <c r="B63" t="n">
-        <v>92640</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751591</v>
+        <v>751561</v>
       </c>
       <c r="R63" t="n">
-        <v>7265038</v>
+        <v>7265244</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6982,12 +6665,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7014,10 +6697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127273298</v>
+        <v>120707846</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7025,21 +6708,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7049,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751712</v>
+        <v>751608</v>
       </c>
       <c r="R64" t="n">
-        <v>7265215</v>
+        <v>7265298</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7079,12 +6762,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7111,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127273292</v>
+        <v>120707847</v>
       </c>
       <c r="B65" t="n">
-        <v>79053</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751718</v>
+        <v>751658</v>
       </c>
       <c r="R65" t="n">
-        <v>7265230</v>
+        <v>7265332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7176,12 +6859,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7208,10 +6891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127273286</v>
+        <v>121775966</v>
       </c>
       <c r="B66" t="n">
-        <v>79618</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,34 +6902,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751709</v>
+        <v>751517</v>
       </c>
       <c r="R66" t="n">
-        <v>7265163</v>
+        <v>7264897</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7273,12 +6956,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7305,32 +6988,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127273291</v>
+        <v>127273299</v>
       </c>
       <c r="B67" t="n">
-        <v>97351</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7340,10 +7023,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751596</v>
+        <v>751784</v>
       </c>
       <c r="R67" t="n">
-        <v>7265044</v>
+        <v>7265143</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7402,10 +7085,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127273283</v>
+        <v>127273300</v>
       </c>
       <c r="B68" t="n">
-        <v>91272</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7413,21 +7096,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7437,10 +7120,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751713</v>
+        <v>751706</v>
       </c>
       <c r="R68" t="n">
-        <v>7265225</v>
+        <v>7265203</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7499,32 +7182,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127273309</v>
+        <v>120707819</v>
       </c>
       <c r="B69" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7534,10 +7217,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751712</v>
+        <v>751541</v>
       </c>
       <c r="R69" t="n">
-        <v>7265138</v>
+        <v>7265181</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7564,12 +7247,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,10 +7279,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127273282</v>
+        <v>127273285</v>
       </c>
       <c r="B70" t="n">
-        <v>91272</v>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7607,21 +7290,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7314,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751666</v>
+        <v>751714</v>
       </c>
       <c r="R70" t="n">
-        <v>7265285</v>
+        <v>7265192</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,27 +7376,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127273290</v>
+        <v>121775959</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7724,14 +7407,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751721</v>
+        <v>751541</v>
       </c>
       <c r="R71" t="n">
-        <v>7265253</v>
+        <v>7264963</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7758,17 +7441,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7795,10 +7473,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127273285</v>
+        <v>127273290</v>
       </c>
       <c r="B72" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7484,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7830,10 +7508,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751714</v>
+        <v>751721</v>
       </c>
       <c r="R72" t="n">
-        <v>7265192</v>
+        <v>7265253</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7866,6 +7544,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7892,48 +7575,61 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127273303</v>
+        <v>120707824</v>
       </c>
       <c r="B73" t="n">
-        <v>91511</v>
+        <v>57141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751726</v>
+        <v>751695</v>
       </c>
       <c r="R73" t="n">
-        <v>7265134</v>
+        <v>7265275</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7960,12 +7656,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7974,7 +7670,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7993,45 +7688,64 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127273297</v>
+        <v>127059027</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>57141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Björklidforsen, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751706</v>
+        <v>751658</v>
       </c>
       <c r="R74" t="n">
-        <v>7265170</v>
+        <v>7265261</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8058,12 +7772,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8090,45 +7814,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127273306</v>
+        <v>121775973</v>
       </c>
       <c r="B75" t="n">
-        <v>78696</v>
+        <v>57132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751791</v>
+        <v>751549</v>
       </c>
       <c r="R75" t="n">
-        <v>7265139</v>
+        <v>7264968</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8155,12 +7879,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8187,48 +7911,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127273304</v>
+        <v>121775974</v>
       </c>
       <c r="B76" t="n">
-        <v>91364</v>
+        <v>57132</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751715</v>
+        <v>751410</v>
       </c>
       <c r="R76" t="n">
-        <v>7265241</v>
+        <v>7264890</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8255,12 +7976,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8269,7 +7990,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8288,10 +8008,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127273288</v>
+        <v>120707827</v>
       </c>
       <c r="B77" t="n">
-        <v>90385</v>
+        <v>58114</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8299,21 +8019,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8323,10 +8043,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751711</v>
+        <v>751677</v>
       </c>
       <c r="R77" t="n">
-        <v>7265216</v>
+        <v>7265294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8353,12 +8073,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8385,32 +8105,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127273312</v>
+        <v>127273291</v>
       </c>
       <c r="B78" t="n">
-        <v>78435</v>
+        <v>97989</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8420,10 +8140,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751748</v>
+        <v>751596</v>
       </c>
       <c r="R78" t="n">
-        <v>7265109</v>
+        <v>7265044</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8482,10 +8202,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127273314</v>
+        <v>120707841</v>
       </c>
       <c r="B79" t="n">
-        <v>78435</v>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8493,21 +8213,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8517,10 +8237,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>751709</v>
+        <v>751608</v>
       </c>
       <c r="R79" t="n">
-        <v>7265165</v>
+        <v>7265248</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8547,12 +8267,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8579,32 +8299,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127273308</v>
+        <v>120707842</v>
       </c>
       <c r="B80" t="n">
-        <v>92640</v>
+        <v>79085</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8614,10 +8334,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>751724</v>
+        <v>751574</v>
       </c>
       <c r="R80" t="n">
-        <v>7265132</v>
+        <v>7265243</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8644,12 +8364,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8676,32 +8396,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127273289</v>
+        <v>120707843</v>
       </c>
       <c r="B81" t="n">
-        <v>91708</v>
+        <v>79085</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2062</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8711,10 +8431,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>751712</v>
+        <v>751678</v>
       </c>
       <c r="R81" t="n">
-        <v>7265174</v>
+        <v>7265289</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8741,12 +8461,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8773,10 +8493,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127273301</v>
+        <v>121775962</v>
       </c>
       <c r="B82" t="n">
-        <v>91971</v>
+        <v>79085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8784,34 +8504,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5454</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>751732</v>
+        <v>751404</v>
       </c>
       <c r="R82" t="n">
-        <v>7265129</v>
+        <v>7264883</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8838,12 +8558,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8870,10 +8590,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127273300</v>
+        <v>121775963</v>
       </c>
       <c r="B83" t="n">
-        <v>78787</v>
+        <v>79085</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8881,34 +8601,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Björklidforsen, Nb</t>
+          <t>Björkliden-Åbyälven, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>751706</v>
+        <v>751417</v>
       </c>
       <c r="R83" t="n">
-        <v>7265203</v>
+        <v>7264910</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8935,12 +8655,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8970,7 +8690,7 @@
         <v>127273296</v>
       </c>
       <c r="B84" t="n">
-        <v>78788</v>
+        <v>79085</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9064,32 +8784,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127273311</v>
+        <v>127273297</v>
       </c>
       <c r="B85" t="n">
-        <v>92640</v>
+        <v>79085</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9099,10 +8819,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>751722</v>
+        <v>751706</v>
       </c>
       <c r="R85" t="n">
-        <v>7265251</v>
+        <v>7265170</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9161,32 +8881,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127273284</v>
+        <v>127273298</v>
       </c>
       <c r="B86" t="n">
-        <v>91315</v>
+        <v>79085</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9196,10 +8916,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>751598</v>
+        <v>751712</v>
       </c>
       <c r="R86" t="n">
-        <v>7265045</v>
+        <v>7265215</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9258,10 +8978,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127273295</v>
+        <v>120707820</v>
       </c>
       <c r="B87" t="n">
-        <v>92833</v>
+        <v>79917</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9269,21 +8989,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9293,10 +9013,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>751733</v>
+        <v>751607</v>
       </c>
       <c r="R87" t="n">
-        <v>7265129</v>
+        <v>7265329</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9323,12 +9043,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9355,10 +9075,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127273299</v>
+        <v>127273286</v>
       </c>
       <c r="B88" t="n">
-        <v>78787</v>
+        <v>79917</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9366,21 +9086,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9390,10 +9110,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>751784</v>
+        <v>751709</v>
       </c>
       <c r="R88" t="n">
-        <v>7265143</v>
+        <v>7265163</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 36307-2023 artfynd.xlsx
+++ b/artfynd/A 36307-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707857</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707858</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775990</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273305</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775967</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273304</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120760993</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273302</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707821</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707822</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707834</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707835</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707836</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273289</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273294</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273295</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273282</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273283</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707839</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707840</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707859</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707860</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707861</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707862</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707863</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707864</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707865</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707866</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4172,6 +4352,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707867</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4269,6 +4454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273307</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4366,6 +4556,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273308</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4463,6 +4658,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273309</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4560,6 +4760,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273310</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4657,6 +4862,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273311</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4754,6 +4964,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707828</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4851,6 +5066,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707829</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707830</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707817</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,6 +5372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707818</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5239,6 +5474,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273284</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5336,6 +5576,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273301</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5433,6 +5678,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775975</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5530,6 +5780,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707851</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5627,6 +5882,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707852</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5724,6 +5984,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775976</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5821,6 +6086,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775977</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5918,6 +6188,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775978</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6015,6 +6290,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775979</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6112,6 +6392,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775983</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6209,6 +6494,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273292</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6306,6 +6596,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707869</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6403,6 +6698,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273312</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6500,6 +6800,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273314</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6597,6 +6902,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707844</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6694,6 +7004,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707845</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6791,6 +7106,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707846</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6888,6 +7208,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707847</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6985,6 +7310,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775966</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7082,6 +7412,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273299</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7179,6 +7514,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273300</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7276,6 +7616,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707819</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7373,6 +7718,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273285</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7470,6 +7820,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775959</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7572,6 +7927,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273290</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7685,6 +8045,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707824</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7811,6 +8176,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127059027</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7908,6 +8278,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775973</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8005,6 +8380,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775974</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8102,6 +8482,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707827</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8199,6 +8584,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273291</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8296,6 +8686,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707841</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8393,6 +8788,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707842</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8490,6 +8890,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707843</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8587,6 +8992,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775962</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8684,6 +9094,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121775963</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8781,6 +9196,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273296</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8878,6 +9298,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273297</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8975,6 +9400,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273298</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9072,6 +9502,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120707820</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9169,8 +9604,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>